--- a/labs/lab-07-interactive-dashboard/data/BrightPath_Recruitment_Dashboard_Data.xlsx
+++ b/labs/lab-07-interactive-dashboard/data/BrightPath_Recruitment_Dashboard_Data.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>KPI definitions</t>
